--- a/tests/test_excelparser/onto_update_only_classes.xlsx
+++ b/tests/test_excelparser/onto_update_only_classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\flb\projects\Team4.0\EMMOntoPy\tests\test_excelparser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\flb\projects\interoperability_tools\EMMOntoPy\tests\test_excelparser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C9AE6A-5517-4B1D-9204-393374EEAF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FF9BE1-FC94-4C27-B2AA-8C285F3F3589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-47055" yWindow="-5730" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-49260" yWindow="-4140" windowWidth="34470" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
     <t>SpecialPattern</t>
   </si>
   <si>
-    <t>https://w3id.org/emmo/inferred</t>
+    <t>https://raw.githubusercontent.com/emmo-repo/EMMOntoPy/refs/heads/master/tests/testonto/emmo/emmo-squashed.ttl</t>
   </si>
 </sst>
 </file>
@@ -1020,9 +1020,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{85EFD210-C177-4421-B2EE-E05889C8F753}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
